--- a/output/yearly_total_coral_cover_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_50_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254522804152868</v>
+        <v>1.253423246724111</v>
       </c>
       <c r="C3" t="n">
-        <v>4.599052971223487</v>
+        <v>4.596686959256252</v>
       </c>
       <c r="D3" t="n">
-        <v>6.035897880630018</v>
+        <v>6.02456851212301</v>
       </c>
       <c r="E3" t="n">
-        <v>11.88947365600637</v>
+        <v>11.87467871810337</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.383672261097139</v>
+        <v>1.380729568522252</v>
       </c>
       <c r="C4" t="n">
-        <v>5.054596331390648</v>
+        <v>5.065143837073039</v>
       </c>
       <c r="D4" t="n">
-        <v>6.255605356729364</v>
+        <v>6.273905433999801</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69387394921715</v>
+        <v>12.71977883959509</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.564220437620924</v>
+        <v>1.56791958771873</v>
       </c>
       <c r="C5" t="n">
-        <v>5.669216132910074</v>
+        <v>5.66070282372795</v>
       </c>
       <c r="D5" t="n">
-        <v>6.554778442171165</v>
+        <v>6.515714271809247</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78821501270216</v>
+        <v>13.74433668325593</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.774825641960096</v>
+        <v>1.787427990558441</v>
       </c>
       <c r="C6" t="n">
-        <v>6.439146315599299</v>
+        <v>6.4357107345987</v>
       </c>
       <c r="D6" t="n">
-        <v>6.912569786337241</v>
+        <v>6.838204355406401</v>
       </c>
       <c r="E6" t="n">
-        <v>15.12654174389664</v>
+        <v>15.06134308056354</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.014765106768961</v>
+        <v>2.040860633665692</v>
       </c>
       <c r="C7" t="n">
-        <v>7.357131058863875</v>
+        <v>7.37005571613855</v>
       </c>
       <c r="D7" t="n">
-        <v>7.303785119874675</v>
+        <v>7.190882052741415</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67568128550751</v>
+        <v>16.60179840254566</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.262759278713623</v>
+        <v>1.286874663987537</v>
       </c>
       <c r="C8" t="n">
-        <v>5.021268032098412</v>
+        <v>5.11633921946351</v>
       </c>
       <c r="D8" t="n">
-        <v>5.632389200844561</v>
+        <v>5.426467911752742</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9164165116566</v>
+        <v>11.82968179520379</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.602977385165314</v>
+        <v>1.637448682979119</v>
       </c>
       <c r="C9" t="n">
-        <v>6.104549761878404</v>
+        <v>6.362130977864425</v>
       </c>
       <c r="D9" t="n">
-        <v>6.159808520733947</v>
+        <v>5.942448993572429</v>
       </c>
       <c r="E9" t="n">
-        <v>13.86733566777766</v>
+        <v>13.94202865441597</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.963245559508705</v>
+        <v>2.017041428121983</v>
       </c>
       <c r="C10" t="n">
-        <v>7.295431131259202</v>
+        <v>7.797538384168932</v>
       </c>
       <c r="D10" t="n">
-        <v>6.644680034778493</v>
+        <v>6.437949515115795</v>
       </c>
       <c r="E10" t="n">
-        <v>15.9033567255464</v>
+        <v>16.25252932740671</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.338039565324787</v>
+        <v>2.395969511308571</v>
       </c>
       <c r="C11" t="n">
-        <v>8.567829956871135</v>
+        <v>9.351009606959098</v>
       </c>
       <c r="D11" t="n">
-        <v>7.265548801437033</v>
+        <v>6.958296453432024</v>
       </c>
       <c r="E11" t="n">
-        <v>18.17141832363296</v>
+        <v>18.70527557169969</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.736520769515458</v>
+        <v>2.76575139311444</v>
       </c>
       <c r="C12" t="n">
-        <v>9.910777746490032</v>
+        <v>10.94791638988495</v>
       </c>
       <c r="D12" t="n">
-        <v>7.806122865503346</v>
+        <v>7.460557575401433</v>
       </c>
       <c r="E12" t="n">
-        <v>20.45342138150884</v>
+        <v>21.17422535840083</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.119223340959496</v>
+        <v>3.118544149235025</v>
       </c>
       <c r="C13" t="n">
-        <v>11.29972136873831</v>
+        <v>12.57810108658551</v>
       </c>
       <c r="D13" t="n">
-        <v>8.41966623905352</v>
+        <v>7.942503719687069</v>
       </c>
       <c r="E13" t="n">
-        <v>22.83861094875133</v>
+        <v>23.63914895550761</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.795842353039393</v>
+        <v>1.784954770999296</v>
       </c>
       <c r="C14" t="n">
-        <v>8.00031112929247</v>
+        <v>8.729062450154878</v>
       </c>
       <c r="D14" t="n">
-        <v>6.437329514223378</v>
+        <v>6.07178557402412</v>
       </c>
       <c r="E14" t="n">
-        <v>16.23348299655524</v>
+        <v>16.58580279517829</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.865919504168531</v>
+        <v>1.833482560020216</v>
       </c>
       <c r="C15" t="n">
-        <v>8.510466506327283</v>
+        <v>9.428430062229177</v>
       </c>
       <c r="D15" t="n">
-        <v>6.522810286832148</v>
+        <v>6.098656008689357</v>
       </c>
       <c r="E15" t="n">
-        <v>16.89919629732796</v>
+        <v>17.36056863093875</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.18624414511018</v>
+        <v>2.139827113653391</v>
       </c>
       <c r="C16" t="n">
-        <v>9.974154158588853</v>
+        <v>11.07722624412648</v>
       </c>
       <c r="D16" t="n">
-        <v>7.080845499403078</v>
+        <v>6.568706992005686</v>
       </c>
       <c r="E16" t="n">
-        <v>19.24124380310211</v>
+        <v>19.78576034978556</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.768893378557818</v>
+        <v>1.726805854476757</v>
       </c>
       <c r="C17" t="n">
-        <v>9.121300110432607</v>
+        <v>10.14704974678376</v>
       </c>
       <c r="D17" t="n">
-        <v>6.651252338978757</v>
+        <v>6.103849454044822</v>
       </c>
       <c r="E17" t="n">
-        <v>17.54144582796918</v>
+        <v>17.97770505530534</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.046099660328948</v>
+        <v>1.984475356933375</v>
       </c>
       <c r="C18" t="n">
-        <v>10.60367042150599</v>
+        <v>11.8211455670195</v>
       </c>
       <c r="D18" t="n">
-        <v>7.189603510079539</v>
+        <v>6.581018108216941</v>
       </c>
       <c r="E18" t="n">
-        <v>19.83937359191448</v>
+        <v>20.38663903216982</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.080411742592374</v>
+        <v>2.0000851454309</v>
       </c>
       <c r="C19" t="n">
-        <v>11.30763261283617</v>
+        <v>12.61379884595134</v>
       </c>
       <c r="D19" t="n">
-        <v>7.358454297732949</v>
+        <v>6.702067600150574</v>
       </c>
       <c r="E19" t="n">
-        <v>20.74649865316149</v>
+        <v>21.31595159153281</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.34376556425658</v>
+        <v>2.243588028515236</v>
       </c>
       <c r="C20" t="n">
-        <v>13.01116122924523</v>
+        <v>14.47618405838458</v>
       </c>
       <c r="D20" t="n">
-        <v>7.867942086328873</v>
+        <v>7.127507967785929</v>
       </c>
       <c r="E20" t="n">
-        <v>23.22286887983069</v>
+        <v>23.84728005468574</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.406883730093849</v>
+        <v>1.345779752981528</v>
       </c>
       <c r="C21" t="n">
-        <v>9.637719037820514</v>
+        <v>10.60337589719472</v>
       </c>
       <c r="D21" t="n">
-        <v>6.611530826864933</v>
+        <v>5.974032955112266</v>
       </c>
       <c r="E21" t="n">
-        <v>17.65613359477929</v>
+        <v>17.92318860528851</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_50_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253423246724111</v>
+        <v>1.249476620953039</v>
       </c>
       <c r="C3" t="n">
-        <v>4.596686959256252</v>
+        <v>4.685328959472696</v>
       </c>
       <c r="D3" t="n">
-        <v>6.02456851212301</v>
+        <v>6.091072101608689</v>
       </c>
       <c r="E3" t="n">
-        <v>11.87467871810337</v>
+        <v>12.02587768203442</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.380729568522252</v>
+        <v>1.365879189028268</v>
       </c>
       <c r="C4" t="n">
-        <v>5.065143837073039</v>
+        <v>5.277124185156883</v>
       </c>
       <c r="D4" t="n">
-        <v>6.273905433999801</v>
+        <v>6.32870353330264</v>
       </c>
       <c r="E4" t="n">
-        <v>12.71977883959509</v>
+        <v>12.97170690748779</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.56791958771873</v>
+        <v>1.522121827783468</v>
       </c>
       <c r="C5" t="n">
-        <v>5.66070282372795</v>
+        <v>6.057091374682418</v>
       </c>
       <c r="D5" t="n">
-        <v>6.515714271809247</v>
+        <v>6.689290528379749</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74433668325593</v>
+        <v>14.26850373084564</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.787427990558441</v>
+        <v>1.710821724327644</v>
       </c>
       <c r="C6" t="n">
-        <v>6.4357107345987</v>
+        <v>7.01576452342624</v>
       </c>
       <c r="D6" t="n">
-        <v>6.838204355406401</v>
+        <v>6.985264677905874</v>
       </c>
       <c r="E6" t="n">
-        <v>15.06134308056354</v>
+        <v>15.71185092565976</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.040860633665692</v>
+        <v>1.91894902504937</v>
       </c>
       <c r="C7" t="n">
-        <v>7.37005571613855</v>
+        <v>8.104043686578203</v>
       </c>
       <c r="D7" t="n">
-        <v>7.190882052741415</v>
+        <v>7.307022311298947</v>
       </c>
       <c r="E7" t="n">
-        <v>16.60179840254566</v>
+        <v>17.33001502292652</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.286874663987537</v>
+        <v>1.140724991082569</v>
       </c>
       <c r="C8" t="n">
-        <v>5.11633921946351</v>
+        <v>5.669581959493097</v>
       </c>
       <c r="D8" t="n">
-        <v>5.426467911752742</v>
+        <v>5.470279146603932</v>
       </c>
       <c r="E8" t="n">
-        <v>11.82968179520379</v>
+        <v>12.2805860971796</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.637448682979119</v>
+        <v>1.421196111614669</v>
       </c>
       <c r="C9" t="n">
-        <v>6.362130977864425</v>
+        <v>6.967164414816365</v>
       </c>
       <c r="D9" t="n">
-        <v>5.942448993572429</v>
+        <v>5.888043003061224</v>
       </c>
       <c r="E9" t="n">
-        <v>13.94202865441597</v>
+        <v>14.27640352949226</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.017041428121983</v>
+        <v>1.715362899094524</v>
       </c>
       <c r="C10" t="n">
-        <v>7.797538384168932</v>
+        <v>8.376013878571452</v>
       </c>
       <c r="D10" t="n">
-        <v>6.437949515115795</v>
+        <v>6.308099622983343</v>
       </c>
       <c r="E10" t="n">
-        <v>16.25252932740671</v>
+        <v>16.39947640064932</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.395969511308571</v>
+        <v>2.016627797059291</v>
       </c>
       <c r="C11" t="n">
-        <v>9.351009606959098</v>
+        <v>9.905390125089831</v>
       </c>
       <c r="D11" t="n">
-        <v>6.958296453432024</v>
+        <v>6.79353723656708</v>
       </c>
       <c r="E11" t="n">
-        <v>18.70527557169969</v>
+        <v>18.7155551587162</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.76575139311444</v>
+        <v>2.306441155684314</v>
       </c>
       <c r="C12" t="n">
-        <v>10.94791638988495</v>
+        <v>11.45190211188272</v>
       </c>
       <c r="D12" t="n">
-        <v>7.460557575401433</v>
+        <v>7.224819417082339</v>
       </c>
       <c r="E12" t="n">
-        <v>21.17422535840083</v>
+        <v>20.98316268464937</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.118544149235025</v>
+        <v>2.590247065705475</v>
       </c>
       <c r="C13" t="n">
-        <v>12.57810108658551</v>
+        <v>13.01552258608211</v>
       </c>
       <c r="D13" t="n">
-        <v>7.942503719687069</v>
+        <v>7.726558139858372</v>
       </c>
       <c r="E13" t="n">
-        <v>23.63914895550761</v>
+        <v>23.33232779164595</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.784954770999296</v>
+        <v>1.493208805728271</v>
       </c>
       <c r="C14" t="n">
-        <v>8.729062450154878</v>
+        <v>9.144184649418598</v>
       </c>
       <c r="D14" t="n">
-        <v>6.07178557402412</v>
+        <v>5.866629756267665</v>
       </c>
       <c r="E14" t="n">
-        <v>16.58580279517829</v>
+        <v>16.50402321141453</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.833482560020216</v>
+        <v>1.512156536420235</v>
       </c>
       <c r="C15" t="n">
-        <v>9.428430062229177</v>
+        <v>9.689211704908258</v>
       </c>
       <c r="D15" t="n">
-        <v>6.098656008689357</v>
+        <v>5.868495076905733</v>
       </c>
       <c r="E15" t="n">
-        <v>17.36056863093875</v>
+        <v>17.06986331823423</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.139827113653391</v>
+        <v>1.745802672553933</v>
       </c>
       <c r="C16" t="n">
-        <v>11.07722624412648</v>
+        <v>11.31321875727333</v>
       </c>
       <c r="D16" t="n">
-        <v>6.568706992005686</v>
+        <v>6.319107455677977</v>
       </c>
       <c r="E16" t="n">
-        <v>19.78576034978556</v>
+        <v>19.37812888550524</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.726805854476757</v>
+        <v>1.393158897188479</v>
       </c>
       <c r="C17" t="n">
-        <v>10.14704974678376</v>
+        <v>10.24613754257339</v>
       </c>
       <c r="D17" t="n">
-        <v>6.103849454044822</v>
+        <v>5.867798036035719</v>
       </c>
       <c r="E17" t="n">
-        <v>17.97770505530534</v>
+        <v>17.50709447579759</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.984475356933375</v>
+        <v>1.583058355620939</v>
       </c>
       <c r="C18" t="n">
-        <v>11.8211455670195</v>
+        <v>11.87342363227065</v>
       </c>
       <c r="D18" t="n">
-        <v>6.581018108216941</v>
+        <v>6.268537631432224</v>
       </c>
       <c r="E18" t="n">
-        <v>20.38663903216982</v>
+        <v>19.72501961932381</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.0000851454309</v>
+        <v>1.585188748139155</v>
       </c>
       <c r="C19" t="n">
-        <v>12.61379884595134</v>
+        <v>12.63707608401903</v>
       </c>
       <c r="D19" t="n">
-        <v>6.702067600150574</v>
+        <v>6.360105239807324</v>
       </c>
       <c r="E19" t="n">
-        <v>21.31595159153281</v>
+        <v>20.58237007196551</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.243588028515236</v>
+        <v>1.766105215077757</v>
       </c>
       <c r="C20" t="n">
-        <v>14.47618405838458</v>
+        <v>14.46615059684718</v>
       </c>
       <c r="D20" t="n">
-        <v>7.127507967785929</v>
+        <v>6.752362535039137</v>
       </c>
       <c r="E20" t="n">
-        <v>23.84728005468574</v>
+        <v>22.98461834696407</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.345779752981528</v>
+        <v>1.053081492437384</v>
       </c>
       <c r="C21" t="n">
-        <v>10.60337589719472</v>
+        <v>10.64156588288992</v>
       </c>
       <c r="D21" t="n">
-        <v>5.974032955112266</v>
+        <v>5.626592442579319</v>
       </c>
       <c r="E21" t="n">
-        <v>17.92318860528851</v>
+        <v>17.32123981790662</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_50_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_50_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249476620953039</v>
+        <v>2.590537189079588</v>
       </c>
       <c r="C3" t="n">
-        <v>4.685328959472696</v>
+        <v>7.654526939736206</v>
       </c>
       <c r="D3" t="n">
-        <v>6.091072101608689</v>
+        <v>8.154865475429466</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02587768203442</v>
+        <v>18.39992960424526</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.365879189028268</v>
+        <v>1.076821175168305</v>
       </c>
       <c r="C4" t="n">
-        <v>5.277124185156883</v>
+        <v>4.37801227395863</v>
       </c>
       <c r="D4" t="n">
-        <v>6.32870353330264</v>
+        <v>5.861348676333435</v>
       </c>
       <c r="E4" t="n">
-        <v>12.97170690748779</v>
+        <v>11.31618212546037</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.522121827783468</v>
+        <v>1.175969071923381</v>
       </c>
       <c r="C5" t="n">
-        <v>6.057091374682418</v>
+        <v>4.873181234985779</v>
       </c>
       <c r="D5" t="n">
-        <v>6.689290528379749</v>
+        <v>6.162650627642172</v>
       </c>
       <c r="E5" t="n">
-        <v>14.26850373084564</v>
+        <v>12.21180093455133</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.710821724327644</v>
+        <v>1.298665810474492</v>
       </c>
       <c r="C6" t="n">
-        <v>7.01576452342624</v>
+        <v>5.485132089537807</v>
       </c>
       <c r="D6" t="n">
-        <v>6.985264677905874</v>
+        <v>6.573126514557598</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71185092565976</v>
+        <v>13.3569244145699</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.91894902504937</v>
+        <v>1.435526007611322</v>
       </c>
       <c r="C7" t="n">
-        <v>8.104043686578203</v>
+        <v>6.205045636586717</v>
       </c>
       <c r="D7" t="n">
-        <v>7.307022311298947</v>
+        <v>6.953760798055143</v>
       </c>
       <c r="E7" t="n">
-        <v>17.33001502292652</v>
+        <v>14.59433244225318</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.140724991082569</v>
+        <v>1.579019382689069</v>
       </c>
       <c r="C8" t="n">
-        <v>5.669581959493097</v>
+        <v>7.048388894870377</v>
       </c>
       <c r="D8" t="n">
-        <v>5.470279146603932</v>
+        <v>7.489305543026631</v>
       </c>
       <c r="E8" t="n">
-        <v>12.2805860971796</v>
+        <v>16.11671382058608</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.421196111614669</v>
+        <v>1.717905143948851</v>
       </c>
       <c r="C9" t="n">
-        <v>6.967164414816365</v>
+        <v>7.973860160454069</v>
       </c>
       <c r="D9" t="n">
-        <v>5.888043003061224</v>
+        <v>7.933953065868877</v>
       </c>
       <c r="E9" t="n">
-        <v>14.27640352949226</v>
+        <v>17.6257183702718</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.715362899094524</v>
+        <v>1.067503366212769</v>
       </c>
       <c r="C10" t="n">
-        <v>8.376013878571452</v>
+        <v>6.012213123330424</v>
       </c>
       <c r="D10" t="n">
-        <v>6.308099622983343</v>
+        <v>6.272346812524701</v>
       </c>
       <c r="E10" t="n">
-        <v>16.39947640064932</v>
+        <v>13.3520633020679</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.016627797059291</v>
+        <v>1.007734565978224</v>
       </c>
       <c r="C11" t="n">
-        <v>9.905390125089831</v>
+        <v>6.170254868760075</v>
       </c>
       <c r="D11" t="n">
-        <v>6.79353723656708</v>
+        <v>6.20870010885838</v>
       </c>
       <c r="E11" t="n">
-        <v>18.7155551587162</v>
+        <v>13.38668954359668</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.306441155684314</v>
+        <v>1.098143712062312</v>
       </c>
       <c r="C12" t="n">
-        <v>11.45190211188272</v>
+        <v>7.13618661749147</v>
       </c>
       <c r="D12" t="n">
-        <v>7.224819417082339</v>
+        <v>6.747591241196498</v>
       </c>
       <c r="E12" t="n">
-        <v>20.98316268464937</v>
+        <v>14.98192157075028</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.590247065705475</v>
+        <v>0.878448210805961</v>
       </c>
       <c r="C13" t="n">
-        <v>13.01552258608211</v>
+        <v>6.674912458651107</v>
       </c>
       <c r="D13" t="n">
-        <v>7.726558139858372</v>
+        <v>6.248598335558971</v>
       </c>
       <c r="E13" t="n">
-        <v>23.33232779164595</v>
+        <v>13.80195900501604</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.493208805728271</v>
+        <v>0.9658924788232245</v>
       </c>
       <c r="C14" t="n">
-        <v>9.144184649418598</v>
+        <v>7.72691402861382</v>
       </c>
       <c r="D14" t="n">
-        <v>5.866629756267665</v>
+        <v>6.795667426273464</v>
       </c>
       <c r="E14" t="n">
-        <v>16.50402321141453</v>
+        <v>15.48847393371051</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.512156536420235</v>
+        <v>0.9518338516984102</v>
       </c>
       <c r="C15" t="n">
-        <v>9.689211704908258</v>
+        <v>8.272215973460668</v>
       </c>
       <c r="D15" t="n">
-        <v>5.868495076905733</v>
+        <v>6.981679163797106</v>
       </c>
       <c r="E15" t="n">
-        <v>17.06986331823423</v>
+        <v>16.20572898895619</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.745802672553933</v>
+        <v>1.057784063940726</v>
       </c>
       <c r="C16" t="n">
-        <v>11.31321875727333</v>
+        <v>9.655351226588785</v>
       </c>
       <c r="D16" t="n">
-        <v>6.319107455677977</v>
+        <v>7.542316007784291</v>
       </c>
       <c r="E16" t="n">
-        <v>19.37812888550524</v>
+        <v>18.2554512983138</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.393158897188479</v>
+        <v>0.6437319696746335</v>
       </c>
       <c r="C17" t="n">
-        <v>10.24613754257339</v>
+        <v>7.327833586837491</v>
       </c>
       <c r="D17" t="n">
-        <v>5.867798036035719</v>
+        <v>6.364159857825864</v>
       </c>
       <c r="E17" t="n">
-        <v>17.50709447579759</v>
+        <v>14.33572541433799</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.583058355620939</v>
+        <v>0.5128453657444488</v>
       </c>
       <c r="C18" t="n">
-        <v>11.87342363227065</v>
+        <v>6.391472078958009</v>
       </c>
       <c r="D18" t="n">
-        <v>6.268537631432224</v>
+        <v>5.946328034898421</v>
       </c>
       <c r="E18" t="n">
-        <v>19.72501961932381</v>
+        <v>12.85064547960088</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.585188748139155</v>
+        <v>0.60712259778327</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63707608401903</v>
+        <v>7.896697476586262</v>
       </c>
       <c r="D19" t="n">
-        <v>6.360105239807324</v>
+        <v>6.632687489891451</v>
       </c>
       <c r="E19" t="n">
-        <v>20.58237007196551</v>
+        <v>15.13650756426098</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.766105215077757</v>
+        <v>0.7008893210158829</v>
       </c>
       <c r="C20" t="n">
-        <v>14.46615059684718</v>
+        <v>9.481110644039061</v>
       </c>
       <c r="D20" t="n">
-        <v>6.752362535039137</v>
+        <v>7.347753247756658</v>
       </c>
       <c r="E20" t="n">
-        <v>22.98461834696407</v>
+        <v>17.5297532128116</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.053081492437384</v>
+        <v>0.785476703213788</v>
       </c>
       <c r="C21" t="n">
-        <v>10.64156588288992</v>
+        <v>11.20335137169107</v>
       </c>
       <c r="D21" t="n">
-        <v>5.626592442579319</v>
+        <v>8.034299234813496</v>
       </c>
       <c r="E21" t="n">
-        <v>17.32123981790662</v>
+        <v>20.02312730971835</v>
       </c>
     </row>
   </sheetData>
